--- a/demo-data/Approval_Matrix.xlsx
+++ b/demo-data/Approval_Matrix.xlsx
@@ -1049,17 +1049,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>POL-MARGIN-60</t>
+          <t>POL-MARGIN-FD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gross Margin: Finance</t>
+          <t>Product Margin: Finance Trigger</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estimated gross margin below configured threshold</t>
+          <t>Deal margin below product weighted target margin less 10 percentage points</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>&lt; 60%</t>
+          <t>Target Gross Margin % - 10%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1100,24 +1100,24 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Configurable margin threshold.</t>
+          <t>Dynamic threshold calculated from Product Master target margin.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>POL-MARGIN-50</t>
+          <t>POL-MARGIN-FD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gross Margin: Executive</t>
+          <t>Product Margin: Finance Trigger</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estimated gross margin below configured threshold</t>
+          <t>Deal margin below product weighted target margin less 10 percentage points</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>&lt; 50%</t>
+          <t>Target Gross Margin % - 10%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1158,24 +1158,24 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Configurable margin threshold.</t>
+          <t>Dynamic threshold calculated from Product Master target margin.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>POL-MARGIN-50</t>
+          <t>POL-MARGIN-GM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gross Margin: Executive</t>
+          <t>Product Margin: General Manager Trigger</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estimated gross margin below configured threshold</t>
+          <t>Deal margin below product weighted target margin less 20 percentage points</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>&lt; 50%</t>
+          <t>Target Gross Margin % - 20%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Configurable margin threshold.</t>
+          <t>Dynamic threshold calculated from Product Master target margin.</t>
         </is>
       </c>
     </row>

--- a/demo-data/Approval_Matrix.xlsx
+++ b/demo-data/Approval_Matrix.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approval Matrix" sheetId="1" r:id="R0c8772caaf334ebe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles" sheetId="2" r:id="Rb1c494a6d9a94902"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approval Matrix" sheetId="1" r:id="Rd25627ed96204571"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles" sheetId="2" r:id="R7ed64fb74a0b4d37"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,7 +14,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -31,8 +31,26 @@
       <x:color rgb="FF334155"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF475569"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -49,6 +67,26 @@
         <x:fgColor rgb="FFEEF3F7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F6B82"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF174F73"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F6B82"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF174F73"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -56,7 +94,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -74,6 +112,30 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -82,7 +144,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ApprovalMatrix" displayName="ApprovalMatrix" ref="A4:I20" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ApprovalMatrix" displayName="ApprovalMatrix" ref="A4:I21" headerRowCount="1">
+  <x:autoFilter ref="A4:I21"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Policy ID"/>
     <x:tableColumn id="2" name="Policy Name"/>
@@ -99,7 +162,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ApprovalRoles" displayName="ApprovalRoles" ref="A4:F13" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="ApprovalRoles" displayName="ApprovalRoles" ref="A4:F12" headerRowCount="1">
+  <x:autoFilter ref="A4:F12"/>
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="Role"/>
     <x:tableColumn id="2" name="Purpose"/>
@@ -308,68 +372,68 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="31" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="55" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="31" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="50" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="31.5" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21.75" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="10.75" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="16" t="str">
         <x:v>Approval Matrix - Commercial Deal Desk</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-      <x:c r="F1" s="4"/>
-      <x:c r="G1" s="4"/>
-      <x:c r="H1" s="4"/>
-      <x:c r="I1" s="4"/>
+      <x:c r="B1" s="16"/>
+      <x:c r="C1" s="16"/>
+      <x:c r="D1" s="16"/>
+      <x:c r="E1" s="16"/>
+      <x:c r="F1" s="16"/>
+      <x:c r="G1" s="16"/>
+      <x:c r="H1" s="16"/>
+      <x:c r="I1" s="16"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="7" t="str">
-        <x:v>Deterministic, configurable routing rules for commercial deal approvals.</x:v>
-      </x:c>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
-      <x:c r="G2" s="7"/>
-      <x:c r="H2" s="7"/>
-      <x:c r="I2" s="7"/>
+      <x:c r="A2" s="14" t="str">
+        <x:v>Configurable routing: Sales review, parallel specialist review, then executive review when triggered.</x:v>
+      </x:c>
+      <x:c r="B2" s="14"/>
+      <x:c r="C2" s="14"/>
+      <x:c r="D2" s="14"/>
+      <x:c r="E2" s="14"/>
+      <x:c r="F2" s="14"/>
+      <x:c r="G2" s="14"/>
+      <x:c r="H2" s="14"/>
+      <x:c r="I2" s="14"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="8" t="str">
+      <x:c r="A4" s="15" t="str">
         <x:v>Policy ID</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
+      <x:c r="B4" s="15" t="str">
         <x:v>Policy Name</x:v>
       </x:c>
-      <x:c r="C4" s="8" t="str">
+      <x:c r="C4" s="15" t="str">
         <x:v>Condition</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="D4" s="15" t="str">
         <x:v>Discount Trigger</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str">
+      <x:c r="E4" s="15" t="str">
         <x:v>Value / Margin Trigger</x:v>
       </x:c>
-      <x:c r="F4" s="8" t="str">
+      <x:c r="F4" s="15" t="str">
         <x:v>Required Role</x:v>
       </x:c>
-      <x:c r="G4" s="8" t="str">
+      <x:c r="G4" s="15" t="str">
         <x:v>Sequence</x:v>
       </x:c>
-      <x:c r="H4" s="8" t="str">
+      <x:c r="H4" s="15" t="str">
         <x:v>SLA Hours</x:v>
       </x:c>
-      <x:c r="I4" s="8" t="str">
+      <x:c r="I4" s="15" t="str">
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
@@ -381,7 +445,7 @@
         <x:v>Discount Tier: Standard</x:v>
       </x:c>
       <x:c r="C5" s="8" t="str">
-        <x:v>Weighted discount is within standard tier</x:v>
+        <x:v>Requested total discount is within the standard tier</x:v>
       </x:c>
       <x:c r="D5" s="8" t="str">
         <x:v>&lt;= 7%</x:v>
@@ -399,56 +463,56 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="I5" s="8" t="str">
-        <x:v>Configurable discount threshold.</x:v>
+        <x:v>Requested total discount is measured from Gross Price.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="8" t="str">
-        <x:v>POL-DISC-MED</x:v>
+        <x:v>POL-DISC-LOW</x:v>
       </x:c>
       <x:c r="B6" s="8" t="str">
-        <x:v>Discount Tier: Governance</x:v>
+        <x:v>Discount Tier: Standard</x:v>
       </x:c>
       <x:c r="C6" s="8" t="str">
-        <x:v>Weighted discount requires cross-functional governance</x:v>
+        <x:v>Requested total discount is within the standard tier</x:v>
       </x:c>
       <x:c r="D6" s="8" t="str">
-        <x:v>&gt; 7% and &lt;= 15%</x:v>
+        <x:v>&lt;= 7%</x:v>
       </x:c>
       <x:c r="E6" s="8" t="str">
         <x:v>Any</x:v>
       </x:c>
       <x:c r="F6" s="8" t="str">
-        <x:v>Sales Manager</x:v>
+        <x:v>Pricing Governance Owner</x:v>
       </x:c>
       <x:c r="G6" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H6" s="8" t="n">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I6" s="8" t="str">
-        <x:v>Configurable discount threshold.</x:v>
+        <x:v>Runs in parallel with Finance review.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="8" t="str">
-        <x:v>POL-DISC-MED</x:v>
+        <x:v>POL-DISC-LOW</x:v>
       </x:c>
       <x:c r="B7" s="8" t="str">
-        <x:v>Discount Tier: Governance</x:v>
+        <x:v>Discount Tier: Standard</x:v>
       </x:c>
       <x:c r="C7" s="8" t="str">
-        <x:v>Weighted discount requires cross-functional governance</x:v>
+        <x:v>Requested total discount is within the standard tier</x:v>
       </x:c>
       <x:c r="D7" s="8" t="str">
-        <x:v>&gt; 7% and &lt;= 15%</x:v>
+        <x:v>&lt;= 7%</x:v>
       </x:c>
       <x:c r="E7" s="8" t="str">
         <x:v>Any</x:v>
       </x:c>
       <x:c r="F7" s="8" t="str">
-        <x:v>Pricing Governance Owner</x:v>
+        <x:v>Finance Director</x:v>
       </x:c>
       <x:c r="G7" s="8" t="n">
         <x:v>2</x:v>
@@ -457,36 +521,36 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I7" s="8" t="str">
-        <x:v>Configurable discount threshold.</x:v>
+        <x:v>Runs in parallel with Pricing Governance review.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="8" t="str">
-        <x:v>POL-DISC-MED</x:v>
+        <x:v>POL-DISC-LOW</x:v>
       </x:c>
       <x:c r="B8" s="8" t="str">
-        <x:v>Discount Tier: Governance</x:v>
+        <x:v>Discount Tier: Standard</x:v>
       </x:c>
       <x:c r="C8" s="8" t="str">
-        <x:v>Weighted discount requires cross-functional governance</x:v>
+        <x:v>Requested total discount is within the standard tier</x:v>
       </x:c>
       <x:c r="D8" s="8" t="str">
-        <x:v>&gt; 7% and &lt;= 15%</x:v>
+        <x:v>&lt;= 7%</x:v>
       </x:c>
       <x:c r="E8" s="8" t="str">
         <x:v>Any</x:v>
       </x:c>
       <x:c r="F8" s="8" t="str">
-        <x:v>Market Access Director</x:v>
+        <x:v>General Manager</x:v>
       </x:c>
       <x:c r="G8" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H8" s="8" t="n">
-        <x:v>48</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I8" s="8" t="str">
-        <x:v>Configurable discount threshold.</x:v>
+        <x:v>Final approver after all required specialist reviews.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -497,7 +561,7 @@
         <x:v>Discount Tier: Governance</x:v>
       </x:c>
       <x:c r="C9" s="8" t="str">
-        <x:v>Weighted discount requires cross-functional governance</x:v>
+        <x:v>Requested total discount requires specialist review</x:v>
       </x:c>
       <x:c r="D9" s="8" t="str">
         <x:v>&gt; 7% and &lt;= 15%</x:v>
@@ -506,65 +570,65 @@
         <x:v>Any</x:v>
       </x:c>
       <x:c r="F9" s="8" t="str">
-        <x:v>Finance Director</x:v>
+        <x:v>Sales Manager</x:v>
       </x:c>
       <x:c r="G9" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H9" s="8" t="n">
-        <x:v>48</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="I9" s="8" t="str">
-        <x:v>Configurable discount threshold.</x:v>
+        <x:v>Requested total discount is measured from Gross Price.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="8" t="str">
-        <x:v>POL-DISC-HIGH</x:v>
+        <x:v>POL-DISC-MED</x:v>
       </x:c>
       <x:c r="B10" s="8" t="str">
-        <x:v>Discount Tier: Executive</x:v>
+        <x:v>Discount Tier: Governance</x:v>
       </x:c>
       <x:c r="C10" s="8" t="str">
-        <x:v>Weighted discount requires executive approval</x:v>
+        <x:v>Requested total discount requires specialist review</x:v>
       </x:c>
       <x:c r="D10" s="8" t="str">
-        <x:v>&gt; 15%</x:v>
+        <x:v>&gt; 7% and &lt;= 15%</x:v>
       </x:c>
       <x:c r="E10" s="8" t="str">
         <x:v>Any</x:v>
       </x:c>
       <x:c r="F10" s="8" t="str">
-        <x:v>Sales Manager</x:v>
+        <x:v>Pricing Governance Owner</x:v>
       </x:c>
       <x:c r="G10" s="8" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H10" s="8" t="n">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I10" s="8" t="str">
-        <x:v>Configurable discount threshold.</x:v>
+        <x:v>Runs in parallel with other triggered specialist reviews.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="8" t="str">
-        <x:v>POL-DISC-HIGH</x:v>
+        <x:v>POL-DISC-MED</x:v>
       </x:c>
       <x:c r="B11" s="8" t="str">
-        <x:v>Discount Tier: Executive</x:v>
+        <x:v>Discount Tier: Governance</x:v>
       </x:c>
       <x:c r="C11" s="8" t="str">
-        <x:v>Weighted discount requires executive approval</x:v>
+        <x:v>Requested total discount requires specialist review</x:v>
       </x:c>
       <x:c r="D11" s="8" t="str">
-        <x:v>&gt; 15%</x:v>
+        <x:v>&gt; 7% and &lt;= 15%</x:v>
       </x:c>
       <x:c r="E11" s="8" t="str">
         <x:v>Any</x:v>
       </x:c>
       <x:c r="F11" s="8" t="str">
-        <x:v>Pricing Governance Owner</x:v>
+        <x:v>Finance Director</x:v>
       </x:c>
       <x:c r="G11" s="8" t="n">
         <x:v>2</x:v>
@@ -573,36 +637,36 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I11" s="8" t="str">
-        <x:v>Configurable discount threshold.</x:v>
+        <x:v>Runs in parallel with other triggered specialist reviews.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="8" t="str">
-        <x:v>POL-DISC-HIGH</x:v>
+        <x:v>POL-DISC-MED</x:v>
       </x:c>
       <x:c r="B12" s="8" t="str">
-        <x:v>Discount Tier: Executive</x:v>
+        <x:v>Discount Tier: Governance</x:v>
       </x:c>
       <x:c r="C12" s="8" t="str">
-        <x:v>Weighted discount requires executive approval</x:v>
+        <x:v>Requested total discount requires specialist review</x:v>
       </x:c>
       <x:c r="D12" s="8" t="str">
-        <x:v>&gt; 15%</x:v>
+        <x:v>&gt; 7% and &lt;= 15%</x:v>
       </x:c>
       <x:c r="E12" s="8" t="str">
         <x:v>Any</x:v>
       </x:c>
       <x:c r="F12" s="8" t="str">
-        <x:v>Market Access Director</x:v>
+        <x:v>General Manager</x:v>
       </x:c>
       <x:c r="G12" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H12" s="8" t="n">
-        <x:v>48</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I12" s="8" t="str">
-        <x:v>Configurable discount threshold.</x:v>
+        <x:v>Final approver after all required specialist reviews.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -613,7 +677,7 @@
         <x:v>Discount Tier: Executive</x:v>
       </x:c>
       <x:c r="C13" s="8" t="str">
-        <x:v>Weighted discount requires executive approval</x:v>
+        <x:v>Requested total discount requires executive approval</x:v>
       </x:c>
       <x:c r="D13" s="8" t="str">
         <x:v>&gt; 15%</x:v>
@@ -622,16 +686,16 @@
         <x:v>Any</x:v>
       </x:c>
       <x:c r="F13" s="8" t="str">
-        <x:v>Finance Director</x:v>
+        <x:v>Sales Manager</x:v>
       </x:c>
       <x:c r="G13" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H13" s="8" t="n">
-        <x:v>48</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="I13" s="8" t="str">
-        <x:v>Configurable discount threshold.</x:v>
+        <x:v>Requested total discount is measured from Gross Price.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -642,7 +706,7 @@
         <x:v>Discount Tier: Executive</x:v>
       </x:c>
       <x:c r="C14" s="8" t="str">
-        <x:v>Weighted discount requires executive approval</x:v>
+        <x:v>Requested total discount requires executive approval</x:v>
       </x:c>
       <x:c r="D14" s="8" t="str">
         <x:v>&gt; 15%</x:v>
@@ -651,94 +715,94 @@
         <x:v>Any</x:v>
       </x:c>
       <x:c r="F14" s="8" t="str">
-        <x:v>General Manager</x:v>
+        <x:v>Pricing Governance Owner</x:v>
       </x:c>
       <x:c r="G14" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H14" s="8" t="n">
-        <x:v>72</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I14" s="8" t="str">
-        <x:v>Configurable discount threshold.</x:v>
+        <x:v>Runs in parallel with Finance review.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="8" t="str">
-        <x:v>POL-MARGIN-FD</x:v>
+        <x:v>POL-DISC-HIGH</x:v>
       </x:c>
       <x:c r="B15" s="8" t="str">
-        <x:v>Product Margin: Finance Trigger</x:v>
+        <x:v>Discount Tier: Executive</x:v>
       </x:c>
       <x:c r="C15" s="8" t="str">
-        <x:v>Deal margin below product weighted target margin less 10 percentage points</x:v>
+        <x:v>Requested total discount requires executive approval</x:v>
       </x:c>
       <x:c r="D15" s="8" t="str">
-        <x:v>Any</x:v>
+        <x:v>&gt; 15%</x:v>
       </x:c>
       <x:c r="E15" s="8" t="str">
-        <x:v>Target Gross Margin % - 10%</x:v>
+        <x:v>Any</x:v>
       </x:c>
       <x:c r="F15" s="8" t="str">
         <x:v>Finance Director</x:v>
       </x:c>
       <x:c r="G15" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H15" s="8" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="I15" s="8" t="str">
-        <x:v>Dynamic threshold calculated from Product Master target margin.</x:v>
+        <x:v>Runs in parallel with Pricing Governance review.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="8" t="str">
-        <x:v>POL-MARGIN-GM</x:v>
+        <x:v>POL-DISC-HIGH</x:v>
       </x:c>
       <x:c r="B16" s="8" t="str">
-        <x:v>Product Margin: General Manager Trigger</x:v>
+        <x:v>Discount Tier: Executive</x:v>
       </x:c>
       <x:c r="C16" s="8" t="str">
-        <x:v>Deal margin below product weighted target margin less 20 percentage points</x:v>
+        <x:v>Requested total discount requires executive approval</x:v>
       </x:c>
       <x:c r="D16" s="8" t="str">
-        <x:v>Any</x:v>
+        <x:v>&gt; 15%</x:v>
       </x:c>
       <x:c r="E16" s="8" t="str">
-        <x:v>Target Gross Margin % - 20%</x:v>
+        <x:v>Any</x:v>
       </x:c>
       <x:c r="F16" s="8" t="str">
         <x:v>General Manager</x:v>
       </x:c>
       <x:c r="G16" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H16" s="8" t="n">
         <x:v>72</x:v>
       </x:c>
       <x:c r="I16" s="8" t="str">
-        <x:v>Dynamic threshold calculated from Product Master target margin.</x:v>
+        <x:v>Final approver after all required specialist reviews.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="8" t="str">
-        <x:v>POL-PUBLIC-PRICE</x:v>
+        <x:v>POL-MARGIN-FD</x:v>
       </x:c>
       <x:c r="B17" s="8" t="str">
-        <x:v>Public Price Impact</x:v>
+        <x:v>Product Margin: Finance Trigger</x:v>
       </x:c>
       <x:c r="C17" s="8" t="str">
-        <x:v>Deal visibility is Public or impacts public/list price</x:v>
+        <x:v>Deal margin is below product target margin less 10 percentage points</x:v>
       </x:c>
       <x:c r="D17" s="8" t="str">
         <x:v>Any</x:v>
       </x:c>
       <x:c r="E17" s="8" t="str">
-        <x:v>Any</x:v>
+        <x:v>Target Gross Margin % - 10%</x:v>
       </x:c>
       <x:c r="F17" s="8" t="str">
-        <x:v>Pricing Governance Owner</x:v>
+        <x:v>Finance Director</x:v>
       </x:c>
       <x:c r="G17" s="8" t="n">
         <x:v>2</x:v>
@@ -747,76 +811,76 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="I17" s="8" t="str">
-        <x:v>Set deal Visibility to Public to trigger.</x:v>
+        <x:v>Dynamic threshold calculated from Product Master target margin.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="8" t="str">
-        <x:v>POL-PUBLIC-PRICE</x:v>
+        <x:v>POL-MARGIN-GM</x:v>
       </x:c>
       <x:c r="B18" s="8" t="str">
-        <x:v>Public Price Impact</x:v>
+        <x:v>Product Margin: General Manager Trigger</x:v>
       </x:c>
       <x:c r="C18" s="8" t="str">
-        <x:v>Deal visibility is Public or impacts public/list price</x:v>
+        <x:v>Deal margin is below product target margin less 20 percentage points</x:v>
       </x:c>
       <x:c r="D18" s="8" t="str">
         <x:v>Any</x:v>
       </x:c>
       <x:c r="E18" s="8" t="str">
-        <x:v>Any</x:v>
+        <x:v>Target Gross Margin % - 20%</x:v>
       </x:c>
       <x:c r="F18" s="8" t="str">
-        <x:v>Market Access Director</x:v>
+        <x:v>General Manager</x:v>
       </x:c>
       <x:c r="G18" s="8" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H18" s="8" t="n">
-        <x:v>48</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I18" s="8" t="str">
-        <x:v>Set deal Visibility to Public to trigger.</x:v>
+        <x:v>Starts after all required specialist reviews are complete.</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="8" t="str">
-        <x:v>POL-CREDIT-OVERDUE</x:v>
+        <x:v>POL-PUBLIC-PRICE</x:v>
       </x:c>
       <x:c r="B19" s="8" t="str">
-        <x:v>Credit Risk: Overdue Receivables</x:v>
+        <x:v>Public Price Impact</x:v>
       </x:c>
       <x:c r="C19" s="8" t="str">
-        <x:v>Customer has overdue receivables</x:v>
+        <x:v>Deal may affect public or list-price precedent</x:v>
       </x:c>
       <x:c r="D19" s="8" t="str">
         <x:v>Any</x:v>
       </x:c>
       <x:c r="E19" s="8" t="str">
-        <x:v>&gt; 0</x:v>
+        <x:v>Any</x:v>
       </x:c>
       <x:c r="F19" s="8" t="str">
-        <x:v>Finance Director</x:v>
+        <x:v>Pricing Governance Owner</x:v>
       </x:c>
       <x:c r="G19" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H19" s="8" t="n">
         <x:v>48</x:v>
       </x:c>
       <x:c r="I19" s="8" t="str">
-        <x:v>Configurable overdue AR threshold.</x:v>
+        <x:v>Public pricing risk is owned by Pricing Governance.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="8" t="str">
-        <x:v>POL-SUPPLY-SHORTAGE</x:v>
+        <x:v>POL-CREDIT-OVERDUE</x:v>
       </x:c>
       <x:c r="B20" s="8" t="str">
-        <x:v>Supply Risk: Inventory Shortage</x:v>
+        <x:v>Credit Risk: Overdue Receivables</x:v>
       </x:c>
       <x:c r="C20" s="8" t="str">
-        <x:v>Inventory shortage exists for requested lines</x:v>
+        <x:v>Customer is on credit hold or has overdue receivables</x:v>
       </x:c>
       <x:c r="D20" s="8" t="str">
         <x:v>Any</x:v>
@@ -825,16 +889,45 @@
         <x:v>&gt; 0</x:v>
       </x:c>
       <x:c r="F20" s="8" t="str">
-        <x:v>Supply Chain Manager</x:v>
+        <x:v>Finance Director</x:v>
       </x:c>
       <x:c r="G20" s="8" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H20" s="8" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I20" s="8" t="str">
+        <x:v>Finance approval remains mandatory before final approval.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>POL-SUPPLY-SHORTAGE</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>Supply Risk: Inventory Shortage</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>Inventory shortage exists for requested lines</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>Any</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>&gt; 0</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>Operations Manager</x:v>
+      </x:c>
+      <x:c r="G21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H21" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="I20" s="8" t="str">
-        <x:v>Configurable shortage threshold.</x:v>
+      <x:c r="I21" t="str">
+        <x:v>Runs in parallel with other triggered specialist reviews.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -844,7 +937,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R781b22e3f80246d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ab80ecb642a4fd3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -853,51 +946,51 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="55" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="23" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="19" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="60" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="20.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="36" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="36" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="55" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="16" t="str">
         <x:v>Approval Roles and Permissions</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-      <x:c r="F1" s="4"/>
+      <x:c r="B1" s="16"/>
+      <x:c r="C1" s="16"/>
+      <x:c r="D1" s="16"/>
+      <x:c r="E1" s="16"/>
+      <x:c r="F1" s="16"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="7" t="str">
-        <x:v>Demo role definitions for deal intake, visibility, and approval routing.</x:v>
-      </x:c>
-      <x:c r="B2" s="7"/>
-      <x:c r="C2" s="7"/>
-      <x:c r="D2" s="7"/>
-      <x:c r="E2" s="7"/>
-      <x:c r="F2" s="7"/>
+      <x:c r="A2" s="14" t="str">
+        <x:v>Role definitions for deal intake, visibility, specialist review, and administration.</x:v>
+      </x:c>
+      <x:c r="B2" s="14"/>
+      <x:c r="C2" s="14"/>
+      <x:c r="D2" s="14"/>
+      <x:c r="E2" s="14"/>
+      <x:c r="F2" s="14"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="8" t="str">
+      <x:c r="A4" s="15" t="str">
         <x:v>Role</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
+      <x:c r="B4" s="15" t="str">
         <x:v>Purpose</x:v>
       </x:c>
-      <x:c r="C4" s="8" t="str">
+      <x:c r="C4" s="15" t="str">
         <x:v>Scope</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="D4" s="15" t="str">
         <x:v>Example Users</x:v>
       </x:c>
-      <x:c r="E4" s="8" t="str">
+      <x:c r="E4" s="15" t="str">
         <x:v>Can View Margin</x:v>
       </x:c>
-      <x:c r="F4" s="8" t="str">
+      <x:c r="F4" s="15" t="str">
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
@@ -946,7 +1039,7 @@
         <x:v>Sales Manager</x:v>
       </x:c>
       <x:c r="B7" s="8" t="str">
-        <x:v>Review sales rationale and assigned KAM deals</x:v>
+        <x:v>Review commercial rationale and assigned KAM deals</x:v>
       </x:c>
       <x:c r="C7" s="8" t="str">
         <x:v>Assigned KAM team</x:v>
@@ -958,7 +1051,7 @@
         <x:v>Status Only</x:v>
       </x:c>
       <x:c r="F7" s="8" t="str">
-        <x:v>Can view only Above/Below Margin Target, not exact margin or product cost.</x:v>
+        <x:v>Can view Above/Below Margin Target, not exact margin, product cost, or margin trigger reference.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -966,7 +1059,7 @@
         <x:v>Pricing Governance Owner</x:v>
       </x:c>
       <x:c r="B8" s="8" t="str">
-        <x:v>Review pricing thresholds, discount governance, and public price impact</x:v>
+        <x:v>Review total discount, pricing thresholds, and public price precedent</x:v>
       </x:c>
       <x:c r="C8" s="8" t="str">
         <x:v>Global pricing queue</x:v>
@@ -983,16 +1076,16 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="8" t="str">
-        <x:v>Market Access Director</x:v>
+        <x:v>Finance Director</x:v>
       </x:c>
       <x:c r="B9" s="8" t="str">
-        <x:v>Review market access and public/list price impact</x:v>
+        <x:v>Review margin, credit risk, and financial exposure</x:v>
       </x:c>
       <x:c r="C9" s="8" t="str">
-        <x:v>Global market access queue</x:v>
+        <x:v>Global finance queue</x:v>
       </x:c>
       <x:c r="D9" s="8" t="str">
-        <x:v>Marcus Reed</x:v>
+        <x:v>Daniel Ortiz</x:v>
       </x:c>
       <x:c r="E9" s="8" t="str">
         <x:v>Yes</x:v>
@@ -1003,83 +1096,71 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="8" t="str">
-        <x:v>Finance Director</x:v>
+        <x:v>Operations Manager</x:v>
       </x:c>
       <x:c r="B10" s="8" t="str">
-        <x:v>Review margin, credit risk, and financial exposure</x:v>
+        <x:v>Review inventory shortages, allocation, and supply feasibility</x:v>
       </x:c>
       <x:c r="C10" s="8" t="str">
-        <x:v>Global finance queue</x:v>
+        <x:v>Operations queue</x:v>
       </x:c>
       <x:c r="D10" s="8" t="str">
-        <x:v>Daniel Ortiz</x:v>
+        <x:v>Elena Rossi</x:v>
       </x:c>
       <x:c r="E10" s="8" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="F10" s="8" t="str">
-        <x:v>Full visibility.</x:v>
+        <x:v>Can view inventory information; cannot view cost or margin.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="8" t="str">
-        <x:v>Supply Chain Manager</x:v>
+        <x:v>General Manager</x:v>
       </x:c>
       <x:c r="B11" s="8" t="str">
-        <x:v>Review inventory shortages and supply feasibility</x:v>
+        <x:v>Approve executive-level commercial exceptions</x:v>
       </x:c>
       <x:c r="C11" s="8" t="str">
-        <x:v>Supply chain queue</x:v>
+        <x:v>Global executive queue</x:v>
       </x:c>
       <x:c r="D11" s="8" t="str">
-        <x:v>Elena Rossi</x:v>
+        <x:v>Sarah Morgan</x:v>
       </x:c>
       <x:c r="E11" s="8" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="F11" s="8" t="str">
-        <x:v>Can view inventory information; cannot view cost or margin.</x:v>
+        <x:v>Full visibility.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="8" t="str">
-        <x:v>General Manager</x:v>
+        <x:v>System Administrator</x:v>
       </x:c>
       <x:c r="B12" s="8" t="str">
-        <x:v>Approve executive-level commercial exceptions</x:v>
+        <x:v>Manage configuration and reference data</x:v>
       </x:c>
       <x:c r="C12" s="8" t="str">
-        <x:v>Global executive queue</x:v>
+        <x:v>System configuration</x:v>
       </x:c>
       <x:c r="D12" s="8" t="str">
-        <x:v>Sarah Morgan</x:v>
+        <x:v>Admin User</x:v>
       </x:c>
       <x:c r="E12" s="8" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F12" s="8" t="str">
-        <x:v>Full visibility.</x:v>
+        <x:v>Full visibility and configuration rights.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="8" t="str">
-        <x:v>System Administrator</x:v>
-      </x:c>
-      <x:c r="B13" s="8" t="str">
-        <x:v>Manage demo configuration and reference data</x:v>
-      </x:c>
-      <x:c r="C13" s="8" t="str">
-        <x:v>System configuration</x:v>
-      </x:c>
-      <x:c r="D13" s="8" t="str">
-        <x:v>Admin User</x:v>
-      </x:c>
-      <x:c r="E13" s="8" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F13" s="8" t="str">
-        <x:v>Full visibility and configuration rights.</x:v>
-      </x:c>
+      <x:c r="A13" s="8"/>
+      <x:c r="B13" s="8"/>
+      <x:c r="C13" s="8"/>
+      <x:c r="D13" s="8"/>
+      <x:c r="E13" s="8"/>
+      <x:c r="F13" s="8"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1088,7 +1169,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11f54c15d92c426d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30cb52db5ab145a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>